--- a/data/Flow01/hashFiles.xlsx
+++ b/data/Flow01/hashFiles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="12">
   <si>
     <t>hashFileErp</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>13/3/2026</t>
+  </si>
+  <si>
+    <t>14/3/2026</t>
   </si>
 </sst>
 </file>
@@ -378,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -549,6 +552,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Flow01/hashFiles.xlsx
+++ b/data/Flow01/hashFiles.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
+          <t>631397bb57df581f452a161263bedc6e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
+          <t>631397bb57df581f452a161263bedc6e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -462,125 +462,6 @@
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>f69716deaeae87f3970042789e3e33a2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>058c65f29a937c82c9f80d3f656dabcc</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>db669c29cca03f5450e3f05d70c97c86</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
         </is>

--- a/data/Flow01/hashFiles.xlsx
+++ b/data/Flow01/hashFiles.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,142 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
